--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484633_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484633_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.138</v>
+        <v>6.3504</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2034</v>
+        <v>6.1928</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0654</v>
+        <v>0.1576</v>
       </c>
       <c r="G2" t="n">
         <v>1.2144</v>
@@ -610,13 +610,13 @@
         <v>2.3823</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6952</v>
+        <v>0.5172</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3506</v>
+        <v>0.6388</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3446</v>
+        <v>-0.1216</v>
       </c>
       <c r="V2" t="n">
         <v>2.4197</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0669</v>
+        <v>4.1606</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6244</v>
+        <v>3.6934</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4424</v>
+        <v>0.4672</v>
       </c>
       <c r="G3" t="n">
         <v>2.1454</v>
@@ -688,13 +688,13 @@
         <v>1.0995</v>
       </c>
       <c r="S3" t="n">
-        <v>0.822</v>
+        <v>0.9157</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.8548</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0361</v>
+        <v>0.0609</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4896</v>
+        <v>1.6984</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5725</v>
+        <v>1.93</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.083</v>
+        <v>-0.2316</v>
       </c>
       <c r="G4" t="n">
         <v>-1.4928</v>
@@ -766,13 +766,13 @@
         <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4326</v>
+        <v>0.6414</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2398</v>
+        <v>0.1177</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6724</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>1.267</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. MARCO LOPEZ</t>
+          <t>L. RODRIGUEZ CAMPIÑA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3708</v>
+        <v>0.6251</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4391</v>
+        <v>0.6251</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0683</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6705</v>
+        <v>0.6251</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.5705</v>
+        <v>0.6251</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7936</v>
+        <v>0.6251</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1395</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.3459</v>
+        <v>0.6251</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4641</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2395</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2246</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1501</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2399</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0898</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.0251</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPIÑA</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6251</v>
+        <v>0.5152</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6251</v>
+        <v>-0.1802</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.6954</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6251</v>
+        <v>-0.9639</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.6998</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6251</v>
+        <v>-2.6637</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6251</v>
+        <v>0.0959</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.2847</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6251</v>
+        <v>-1.1889</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.0597</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.4151</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-1.4748</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.6874</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.2187</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.4687</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.1246</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.1869</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. BORISOV</t>
+          <t>J. ROIG MESA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4322</v>
+        <v>0.4958</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2334</v>
+        <v>0.4444</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1988</v>
+        <v>0.0514</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5796</v>
+        <v>-0.0584</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2461</v>
+        <v>-1.8857</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3336</v>
+        <v>1.8273</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6523</v>
+        <v>0.2257</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.3162</v>
+        <v>-1.217</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9685</v>
+        <v>1.4427</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.232</v>
+        <v>-0.284</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0701</v>
+        <v>-0.6686</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.3021</v>
+        <v>0.3846</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1991</v>
+        <v>0.5498</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5408</v>
+        <v>0.0043</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9322</v>
+        <v>0.2187</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6086</v>
+        <v>-0.2144</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2878</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6647</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ROIG MESA</t>
+          <t>H. MARCO LOPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0313</v>
+        <v>-0.1537</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0047</v>
+        <v>1.9146</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0266</v>
+        <v>-2.0683</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0584</v>
+        <v>-0.6705</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8857</v>
+        <v>1.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8273</v>
+        <v>-2.5705</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2257</v>
+        <v>0.7936</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.217</v>
+        <v>3.1395</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4427</v>
+        <v>-2.3459</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.284</v>
+        <v>-1.4641</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6686</v>
+        <v>-1.2395</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3846</v>
+        <v>-0.2246</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5498</v>
+        <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4601</v>
+        <v>1.6256</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.221</v>
+        <v>1.7153</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2392</v>
+        <v>-0.0898</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.0251</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.347</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>D. BORISOV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5678</v>
+        <v>-0.3071</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1146</v>
+        <v>-0.2334</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5468</v>
+        <v>-0.0737</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9639</v>
+        <v>-2.5796</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6998</v>
+        <v>-1.2461</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6637</v>
+        <v>-1.3336</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0959</v>
+        <v>0.6523</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2847</v>
+        <v>-1.3162</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1889</v>
+        <v>1.9685</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0597</v>
+        <v>-3.232</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4151</v>
+        <v>0.0701</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4748</v>
+        <v>-3.3021</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9163</v>
+        <v>0.1833</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1833</v>
+        <v>-2.0158</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0995</v>
+        <v>2.1991</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3956</v>
+        <v>0.8015</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7157</v>
+        <v>0.4653</v>
       </c>
       <c r="U9" t="n">
-        <v>0.32</v>
+        <v>0.3361</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1246</v>
+        <v>1.2878</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3115</v>
+        <v>0.6647</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1869</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3548</v>
+        <v>-1.4396</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9879</v>
+        <v>-1.2213</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3669</v>
+        <v>-0.2183</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8929</v>
@@ -1234,13 +1234,13 @@
         <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4098</v>
+        <v>0.325</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6214</v>
+        <v>0.388</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2116</v>
+        <v>-0.063</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3219</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5065</v>
+        <v>-1.7729</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2975</v>
+        <v>0.2293</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.804</v>
+        <v>-2.0022</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3409</v>
@@ -1312,13 +1312,13 @@
         <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4983</v>
+        <v>1.2319</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0415</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4568</v>
+        <v>0.2586</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7477</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9928</v>
+        <v>-4.0639</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1112</v>
+        <v>-3.2318</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8817</v>
+        <v>-0.8321</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3125</v>
@@ -1390,13 +1390,13 @@
         <v>1.6493</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7181</v>
+        <v>0.2108</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7157</v>
+        <v>0.1637</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0024</v>
+        <v>0.0471</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7789</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.732000000000002</v>
+        <v>6.108299999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>8.786399999999999</v>
+        <v>10.1629</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.0547</v>
+        <v>-4.0546</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.3266</v>
+        <v>-7.326600000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>1.969</v>
+        <v>1.968999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>-9.2959</v>
@@ -1468,10 +1468,10 @@
         <v>15.5768</v>
       </c>
       <c r="S13" t="n">
-        <v>5.5846</v>
+        <v>6.9608</v>
       </c>
       <c r="T13" t="n">
-        <v>4.377999999999999</v>
+        <v>5.754300000000001</v>
       </c>
       <c r="U13" t="n">
         <v>1.2063</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. BURJEL PEZZATTI</t>
+          <t>J. CHALER ROMERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1295</v>
+        <v>2.6276</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0144</v>
+        <v>2.9699</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8849</v>
+        <v>-0.3423</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1191</v>
+        <v>2.1394</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0936</v>
+        <v>-0.759</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0255</v>
+        <v>2.8984</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4536</v>
+        <v>3.4661</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5944</v>
+        <v>0.0867</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8592</v>
+        <v>3.3794</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3345</v>
+        <v>-1.3267</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5008</v>
+        <v>-0.8457</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8338</v>
+        <v>-0.481</v>
       </c>
       <c r="P14" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1722</v>
+        <v>-0.4904</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7677</v>
+        <v>-0.313</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.1774</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5504</v>
+        <v>0.0623</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.2907</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2596</v>
+        <v>0.0623</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CHALER ROMERO</t>
+          <t>N. BURJEL PEZZATTI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9209</v>
+        <v>2.3247</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5853</v>
+        <v>2.7259</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6643</v>
+        <v>-0.4011</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1394</v>
+        <v>2.1191</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.759</v>
+        <v>2.0936</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8984</v>
+        <v>0.0255</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4661</v>
+        <v>3.4536</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0867</v>
+        <v>2.5944</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3794</v>
+        <v>0.8592</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3267</v>
+        <v>-1.3345</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8457</v>
+        <v>-0.5008</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.481</v>
+        <v>-0.8338</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1833</v>
+        <v>-0.9163</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.197</v>
+        <v>0.023</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6976</v>
+        <v>0.4793</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4995</v>
+        <v>-0.4563</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0623</v>
+        <v>-0.5504</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.2907</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0623</v>
+        <v>-0.2596</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. RAMON AÑIBARRO</t>
+          <t>A. VILLALBA MOLLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3251</v>
+        <v>0.6875</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3251</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3251</v>
+        <v>0.793</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3251</v>
+        <v>-1.5407</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2.3338</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3251</v>
+        <v>1.5335</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3251</v>
+        <v>-0.576</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.1095</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.9647</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.2243</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.0417</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.1554</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.1137</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.3189</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0519</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VILLALBA MOLLA</t>
+          <t>N. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3218</v>
+        <v>0.3251</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7477</v>
+        <v>0.3251</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4259</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.793</v>
+        <v>0.3251</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5407</v>
+        <v>0.3251</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3338</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5335</v>
+        <v>0.3251</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.576</v>
+        <v>0.3251</v>
       </c>
       <c r="L17" t="n">
-        <v>2.1095</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7403999999999999</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9647</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2243</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.4661</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3241</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0369</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2871</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3189</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0519</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1891</v>
+        <v>0.1148</v>
       </c>
       <c r="E18" t="n">
         <v>0.9699</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7808</v>
+        <v>-0.8551</v>
       </c>
       <c r="G18" t="n">
         <v>0.8086</v>
@@ -1858,13 +1858,13 @@
         <v>0.1833</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1589</v>
+        <v>-0.2332</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3854</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2265</v>
+        <v>0.1521</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6439</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>M. AROCA RUBIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3435</v>
+        <v>-0.0102</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7882</v>
+        <v>0.7224</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4447</v>
+        <v>-0.7325</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3941</v>
+        <v>3.2694</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9265</v>
+        <v>1.0256</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4677</v>
+        <v>2.2437</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4863</v>
+        <v>4.2134</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5695</v>
+        <v>1.3281</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9167999999999999</v>
+        <v>2.8854</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0922</v>
+        <v>-0.944</v>
       </c>
       <c r="N19" t="n">
-        <v>0.357</v>
+        <v>-0.3024</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4492</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.2828</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9321</v>
+        <v>-3.8484</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6493</v>
+        <v>2.0158</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1341</v>
+        <v>-0.8239</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6576</v>
+        <v>-0.2865</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4764</v>
+        <v>-0.5374</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5889</v>
+        <v>-0.6231</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5889</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. AROCA RUBIO</t>
+          <t>S. LOZANO CATALA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7357</v>
+        <v>-0.7294</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5301</v>
+        <v>-0.2536</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2658</v>
+        <v>-0.4758</v>
       </c>
       <c r="G20" t="n">
-        <v>3.2694</v>
+        <v>-0.4043</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0256</v>
+        <v>-0.5003</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2437</v>
+        <v>0.0961</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2134</v>
+        <v>0.0217</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3281</v>
+        <v>0.0217</v>
       </c>
       <c r="L20" t="n">
-        <v>2.8854</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.944</v>
+        <v>-0.4259</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3024</v>
+        <v>-0.522</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.0961</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.8484</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5495</v>
+        <v>-0.6367</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4789</v>
+        <v>-0.2753</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0706</v>
+        <v>-0.3614</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6231</v>
+        <v>0.3115</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.267</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. LOZANO CATALA</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7542</v>
+        <v>-0.7894</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2536</v>
+        <v>-1.1728</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5006</v>
+        <v>0.3834</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4043</v>
+        <v>1.3941</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5003</v>
+        <v>0.9265</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0961</v>
+        <v>0.4677</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0217</v>
+        <v>1.4863</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0217</v>
+        <v>0.5695</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4259</v>
+        <v>-0.0922</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.522</v>
+        <v>0.357</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0961</v>
+        <v>-0.4492</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9321</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6615</v>
+        <v>0.6881</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2753</v>
+        <v>0.273</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3862</v>
+        <v>0.4151</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3115</v>
+        <v>-1.5889</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3115</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3263</v>
+        <v>-1.5027</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.7562</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.474</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0827</v>
@@ -2170,13 +2170,13 @@
         <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3634</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3869</v>
+        <v>-0.2907</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0234</v>
+        <v>-0.2491</v>
       </c>
       <c r="V22" t="n">
         <v>1.3189</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9858</v>
+        <v>-2.387</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4128</v>
+        <v>-1.1244</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.573</v>
+        <v>-1.2627</v>
       </c>
       <c r="G23" t="n">
         <v>-2.049</v>
@@ -2248,13 +2248,13 @@
         <v>1.6493</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7713</v>
+        <v>-1.1725</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8823</v>
+        <v>-0.5939</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.889</v>
+        <v>-0.5787</v>
       </c>
       <c r="V23" t="n">
         <v>1.0177</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4728</v>
+        <v>-3.4698</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8108</v>
+        <v>-1.2916</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6619</v>
+        <v>-2.1782</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9863</v>
@@ -2326,13 +2326,13 @@
         <v>0.5498</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.5177</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5113</v>
+        <v>0.0306</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.032</v>
+        <v>-0.5483</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5993</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7319</v>
+        <v>-2.8088</v>
       </c>
       <c r="E25" t="n">
-        <v>4.0548</v>
+        <v>4.054600000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.7865</v>
+        <v>-6.863300000000001</v>
       </c>
       <c r="G25" t="n">
         <v>7.3264</v>
@@ -2404,13 +2404,13 @@
         <v>10.0791</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.5845</v>
+        <v>-3.6614</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2067</v>
+        <v>-1.2065</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.3781</v>
+        <v>-2.4551</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9762999999999999</v>
